--- a/ri_plus_5036/urdf/initial_joint_properties.xlsx
+++ b/ri_plus_5036/urdf/initial_joint_properties.xlsx
@@ -449,7 +449,7 @@
     <col width="14.4" customWidth="1" min="7" max="7"/>
     <col width="15.6" customWidth="1" min="8" max="8"/>
     <col width="14.4" customWidth="1" min="9" max="9"/>
-    <col width="14.4" customWidth="1" min="10" max="10"/>
+    <col width="15.6" customWidth="1" min="10" max="10"/>
     <col width="14.4" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -591,34 +591,34 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.40794661</v>
+        <v>0.45986342</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-0.00362205</v>
+        <v>-0.16046069</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.0170977</v>
+        <v>-0.01462992</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.026037</v>
+        <v>0.16817732</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.00113124</v>
+        <v>0.00140888</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.554e-05</v>
+        <v>2.993e-05</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-7.025999999999999e-05</v>
+        <v>-8.706e-05</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.00099464</v>
+        <v>0.00130708</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.00018381</v>
+        <v>0.00019281</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.00035636</v>
+        <v>0.00039744</v>
       </c>
     </row>
     <row r="5">
@@ -628,34 +628,34 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.06068055</v>
+        <v>0.0779043</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.01005013</v>
+        <v>0.00943045</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.13e-06</v>
+        <v>-1.957e-05</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.05890115</v>
+        <v>-0.05845552</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.00021231</v>
+        <v>0.0002959</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.46e-05</v>
+        <v>2.264e-05</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.00021592</v>
+        <v>0.00030164</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-2e-08</v>
+        <v>1.2e-07</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>5.96e-06</v>
+        <v>8.790000000000001e-06</v>
       </c>
     </row>
     <row r="6">
@@ -739,34 +739,34 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.40794627</v>
+        <v>0.45512966</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0.00391519</v>
+        <v>-0.00452385</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.01709766</v>
+        <v>0.01478204</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.02619176</v>
+        <v>-0.02874766</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.00112834</v>
+        <v>0.00139558</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-2.575e-05</v>
+        <v>-3.122e-05</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-6.575999999999999e-05</v>
+        <v>-8.995e-05</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.00099044</v>
+        <v>0.00129398</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.0001821</v>
+        <v>-0.00019505</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.00035506</v>
+        <v>0.00039559</v>
       </c>
     </row>
     <row r="9">
@@ -776,34 +776,34 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.06068055</v>
+        <v>0.0779043</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.01005013</v>
+        <v>0.00943045</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.13e-06</v>
+        <v>-1.957e-05</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.05890115</v>
+        <v>-0.05845552</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.00021231</v>
+        <v>0.0002959</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.46e-05</v>
+        <v>2.264e-05</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.00021592</v>
+        <v>0.00030164</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-2e-08</v>
+        <v>1.2e-07</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>5.96e-06</v>
+        <v>8.790000000000001e-06</v>
       </c>
     </row>
     <row r="10">
@@ -887,34 +887,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.40794661</v>
+        <v>0.45986342</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.00379857</v>
+        <v>-0.16046069</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.0170977</v>
+        <v>-0.01462992</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.02604468</v>
+        <v>0.16817732</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.00113096</v>
+        <v>0.00140888</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2.664e-05</v>
+        <v>2.993e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-6.701e-05</v>
+        <v>-8.706e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.00099394</v>
+        <v>0.00130708</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.00018386</v>
+        <v>0.00019281</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.00035594</v>
+        <v>0.00039744</v>
       </c>
     </row>
     <row r="13">
@@ -924,34 +924,34 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.06068055</v>
+        <v>0.0779043</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.01005013</v>
+        <v>0.00943045</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3.13e-06</v>
+        <v>-1.957e-05</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.05890115</v>
+        <v>-0.05845552</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.00021231</v>
+        <v>0.0002959</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.46e-05</v>
+        <v>2.264e-05</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.00021592</v>
+        <v>0.00030164</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-2e-08</v>
+        <v>1.2e-07</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>5.96e-06</v>
+        <v>8.790000000000001e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.40794627</v>
+        <v>0.45512966</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.00391519</v>
+        <v>-0.00452385</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.01709766</v>
+        <v>0.01478204</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.02619176</v>
+        <v>-0.02874766</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.00112834</v>
+        <v>0.00139558</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.575e-05</v>
+        <v>-3.122e-05</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-6.575999999999999e-05</v>
+        <v>-8.995e-05</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.00099044</v>
+        <v>0.00129398</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.0001821</v>
+        <v>-0.00019505</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.00035506</v>
+        <v>0.00039559</v>
       </c>
     </row>
     <row r="17">
@@ -1072,34 +1072,34 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.06096356</v>
+        <v>0.0779043</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.01000348</v>
+        <v>0.00943045</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.11e-06</v>
+        <v>-1.957e-05</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0586277</v>
+        <v>-0.05845552</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0002133</v>
+        <v>0.0002959</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1.477e-05</v>
+        <v>2.264e-05</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.00021693</v>
+        <v>0.00030164</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-2e-08</v>
+        <v>1.2e-07</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>6e-06</v>
+        <v>8.790000000000001e-06</v>
       </c>
     </row>
     <row r="18">
